--- a/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:27:16+00:00</t>
+    <t>2025-10-21T13:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5232,7 +5232,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>269</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>292</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>377</v>
       </c>
@@ -11056,12 +11056,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL85">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:57:20+00:00</t>
+    <t>2025-10-21T14:02:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-location-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T14:02:08+00:00</t>
+    <t>2025-10-21T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
